--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1424,12 +1424,7 @@
         <v>63289977</v>
       </c>
       <c r="B8" t="n">
-        <v>103148</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,10 +1456,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425008.5812048276</v>
+        <v>425009</v>
       </c>
       <c r="R8" t="n">
-        <v>6177294.046538768</v>
+        <v>6177294</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1494,19 +1489,9 @@
           <t>2001-06-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2001-06-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1555,12 +1540,7 @@
         <v>63289366</v>
       </c>
       <c r="B9" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425007.4774916052</v>
+        <v>425007</v>
       </c>
       <c r="R9" t="n">
-        <v>6177393.715259393</v>
+        <v>6177394</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1625,19 +1605,9 @@
           <t>2001-06-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2001-06-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1686,12 +1656,7 @@
         <v>63289367</v>
       </c>
       <c r="B10" t="n">
-        <v>103148</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425007.4774916052</v>
+        <v>425007</v>
       </c>
       <c r="R10" t="n">
-        <v>6177393.715259393</v>
+        <v>6177394</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1756,19 +1721,9 @@
           <t>2001-06-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2001-06-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1817,12 +1772,7 @@
         <v>63289369</v>
       </c>
       <c r="B11" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425007.4774916052</v>
+        <v>425007</v>
       </c>
       <c r="R11" t="n">
-        <v>6177393.715259393</v>
+        <v>6177394</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1887,19 +1837,9 @@
           <t>2001-06-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2001-06-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1948,12 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>96246</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98496</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425007.4774916052</v>
+        <v>425007</v>
       </c>
       <c r="R12" t="n">
-        <v>6177393.715259393</v>
+        <v>6177394</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -2017,19 +1952,9 @@
           <t>2001-06-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2001-06-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2078,12 +2003,7 @@
         <v>63289365</v>
       </c>
       <c r="B13" t="n">
-        <v>96268</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,10 +2031,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425007.4774916052</v>
+        <v>425007</v>
       </c>
       <c r="R13" t="n">
-        <v>6177393.715259393</v>
+        <v>6177394</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2144,19 +2064,9 @@
           <t>2001-06-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2001-06-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>63289977</v>
       </c>
       <c r="B8" t="n">
-        <v>105591</v>
+        <v>105596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>63289366</v>
       </c>
       <c r="B9" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>63289367</v>
       </c>
       <c r="B10" t="n">
-        <v>105591</v>
+        <v>105596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>63289369</v>
       </c>
       <c r="B11" t="n">
-        <v>107112</v>
+        <v>107117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98557</v>
+        <v>98562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>63289365</v>
       </c>
       <c r="B13" t="n">
-        <v>98580</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>63289977</v>
       </c>
       <c r="B8" t="n">
-        <v>105596</v>
+        <v>105604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>63289366</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>63289367</v>
       </c>
       <c r="B10" t="n">
-        <v>105596</v>
+        <v>105604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>63289369</v>
       </c>
       <c r="B11" t="n">
-        <v>107117</v>
+        <v>107125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98562</v>
+        <v>98570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>63289365</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>63289977</v>
       </c>
       <c r="B8" t="n">
-        <v>105604</v>
+        <v>105614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>63289366</v>
       </c>
       <c r="B9" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>63289367</v>
       </c>
       <c r="B10" t="n">
-        <v>105604</v>
+        <v>105614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>63289369</v>
       </c>
       <c r="B11" t="n">
-        <v>107125</v>
+        <v>107135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98570</v>
+        <v>98580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>63289365</v>
       </c>
       <c r="B13" t="n">
-        <v>98593</v>
+        <v>98603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -2115,12 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>96268</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425049.4380000998</v>
+        <v>425049</v>
       </c>
       <c r="R14" t="n">
-        <v>6177405.94113851</v>
+        <v>6177406</v>
       </c>
       <c r="S14" t="n">
         <v>62</v>
@@ -2184,19 +2179,9 @@
           <t>2015-06-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98885</v>
+        <v>98887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98887</v>
+        <v>98891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98580</v>
+        <v>98868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98868</v>
+        <v>98881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98891</v>
+        <v>98904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98881</v>
+        <v>98882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98904</v>
+        <v>98905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98882</v>
+        <v>98885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98905</v>
+        <v>98908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98885</v>
+        <v>98899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98908</v>
+        <v>98922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98899</v>
+        <v>98900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98922</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -1888,7 +1888,7 @@
         <v>63289373</v>
       </c>
       <c r="B12" t="n">
-        <v>98900</v>
+        <v>98914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>53807006</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17778-2025 artfynd.xlsx
+++ b/artfynd/A 17778-2025 artfynd.xlsx
@@ -675,67 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>488187</v>
+        <v>53807006</v>
       </c>
       <c r="B2" t="n">
-        <v>106807</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1174</v>
+        <v>514</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Majnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Dactylorhiza majalis subsp. majalis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ryssgård, 850 m öster, Sk</t>
+          <t>Fränninge, Solhälls rikkärr, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425047</v>
+        <v>425049</v>
       </c>
       <c r="R2" t="n">
-        <v>6177423</v>
+        <v>6177406</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,24 +737,19 @@
           <t>Fränninge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Sbo-0322</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-06-02</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-06-02</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kärr i betesmark. Rikligt med majnycklar.</t>
+          <t>Talrik både i kanterna och ute i kärret.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,81 +760,60 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>kärraktig betesmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53807168</v>
+        <v>63289365</v>
       </c>
       <c r="B3" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221049</v>
+        <v>514</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Majnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza majalis subsp. majalis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fränninge, Solhälls rikkärr, Sk</t>
+          <t>850m O Ryssgård, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425049.4380000998</v>
+        <v>425007</v>
       </c>
       <c r="R3" t="n">
-        <v>6177405.94113851</v>
+        <v>6177394</v>
       </c>
       <c r="S3" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,31 +858,40 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>frisk betesmark</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>SkFlora    673873</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alf Porenius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53807133</v>
+        <v>53894654</v>
       </c>
       <c r="B4" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,16 +899,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221137</v>
+        <v>1012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Lysimachia nemorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -968,17 +926,17 @@
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fränninge, Solhälls rikkärr, Sk</t>
+          <t>Fränninge sollhälls hagmark väster om  rikkärret, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425049.4380000998</v>
+        <v>424992</v>
       </c>
       <c r="R4" t="n">
-        <v>6177405.94113851</v>
+        <v>6177422</v>
       </c>
       <c r="S4" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,27 +960,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ny lokal för arten. En del af kärret är en fin liten rikkärrsyta och det ligger i mycket trevligt skogsbetemiljö. Kärret är inte känd i rikkärrsnventeringen. Betesmarken ägs av gården Solhäll en bit söder om. Ytan med riktigt rikkärr är liten, men där växer majvivan dock i ett bra bestånd. Mot norröst blir kärret markant fattigare. Se miljöbilder.</t>
+          <t>Med Envina-gruppen (danska kommunbiologer)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53807052</v>
+        <v>63289367</v>
       </c>
       <c r="B5" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,16 +1008,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1174</v>
+        <v>1012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Lysimachia nemorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,26 +1026,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fränninge, Solhälls rikkärr, Sk</t>
+          <t>850m O Ryssgård, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425049.4380000998</v>
+        <v>425007</v>
       </c>
       <c r="R5" t="n">
-        <v>6177405.94113851</v>
+        <v>6177394</v>
       </c>
       <c r="S5" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,27 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Här och var i sydvästra änden av kärret, tillsammans med majnycklar men utanför ytan med majvivor. Se miljöbild.</t>
+          <t>Lysimachia nemorum/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,31 +1083,40 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>frisk betesmark</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>SkFlora    673875</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alf Porenius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53894654</v>
+        <v>63289977</v>
       </c>
       <c r="B6" t="n">
-        <v>103148</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,26 +1142,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fränninge sollhälls hagmark väster om  rikkärret, Sk</t>
+          <t>800m OSO Rydsgård, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424992.1698640745</v>
+        <v>425009</v>
       </c>
       <c r="R6" t="n">
-        <v>6177422.12826406</v>
+        <v>6177294</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,27 +1178,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Med Envina-gruppen (danska kommunbiologer)</t>
+          <t>Lysimachia nemorum/2D6e0344/Fränninge s:n/RGl/ /Rune Gerell,Sjöbo</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,31 +1199,40 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>alskog</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>SkFlora    690511</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53899075</v>
+        <v>462193</v>
       </c>
       <c r="B7" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107664</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,26 +1258,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fränninge Solhälls hagmark nordväst, Sk</t>
+          <t>Ryssgård, 850 m öster, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424886.0743137521</v>
+        <v>425047</v>
       </c>
       <c r="R7" t="n">
-        <v>6177518.538117019</v>
+        <v>6177423</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,29 +1292,24 @@
           <t>Fränninge</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>M-Sbo-0322</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-06-10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fläckvist ganska talrik</t>
+          <t>2D6e0444</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,26 +1320,35 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>kärraktig betesmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alf Porenius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63289977</v>
+        <v>53807052</v>
       </c>
       <c r="B8" t="n">
-        <v>105614</v>
+        <v>107664</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,16 +1356,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1012</v>
+        <v>1174</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lysimachia nemorum</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1450,19 +1374,26 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>800m OSO Rydsgård, Sk</t>
+          <t>Fränninge, Solhälls rikkärr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425009</v>
+        <v>425049</v>
       </c>
       <c r="R8" t="n">
-        <v>6177294</v>
+        <v>6177406</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,17 +1417,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2001-06-25</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2001-06-25</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lysimachia nemorum/2D6e0344/Fränninge s:n/RGl/ /Rune Gerell,Sjöbo</t>
+          <t>Här och var i sydvästra änden av kärret, tillsammans med majnycklar men utanför ytan med majvivor. Se miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,40 +1438,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>alskog</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>SkFlora    690511</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rune Gerell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63289366</v>
+        <v>53899075</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>107664</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,37 +1465,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222322</v>
+        <v>1174</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>850m O Ryssgård, Sk</t>
+          <t>Fränninge Solhälls hagmark nordväst, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425007</v>
+        <v>424886</v>
       </c>
       <c r="R9" t="n">
-        <v>6177394</v>
+        <v>6177519</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,17 +1526,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2001-06-10</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2001-06-10</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Carex hostiana/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
+          <t>Fläckvist ganska talrik</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,40 +1547,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>frisk betesmark</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>SkFlora    673874</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alf Porenius</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63289367</v>
+        <v>63289369</v>
       </c>
       <c r="B10" t="n">
-        <v>105614</v>
+        <v>107663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,16 +1574,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1012</v>
+        <v>1174</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lysimachia nemorum</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1728,7 +1638,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lysimachia nemorum/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
+          <t>Pedicularis sylvatica/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,12 +1652,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>frisk betesmark</t>
+          <t>kärraktig betesmark</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>SkFlora    673875</t>
+          <t>SkFlora    673877</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1769,27 +1679,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63289369</v>
+        <v>53807168</v>
       </c>
       <c r="B11" t="n">
-        <v>107135</v>
+        <v>111129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1174</v>
+        <v>221049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1798,19 +1708,22 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>850m O Ryssgård, Sk</t>
+          <t>Fränninge, Solhälls rikkärr, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425007</v>
+        <v>425049</v>
       </c>
       <c r="R11" t="n">
-        <v>6177394</v>
+        <v>6177406</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,17 +1747,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2001-06-10</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2001-06-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Pedicularis sylvatica/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,77 +1763,71 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>kärraktig betesmark</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>SkFlora    673877</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alf Porenius</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63289373</v>
+        <v>53807133</v>
       </c>
       <c r="B12" t="n">
-        <v>98924</v>
+        <v>106140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>850m O Ryssgård, Sk</t>
+          <t>Fränninge, Solhälls rikkärr, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425007</v>
+        <v>425049</v>
       </c>
       <c r="R12" t="n">
-        <v>6177394</v>
+        <v>6177406</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1949,17 +1851,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2001-06-19</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2001-06-19</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata ssp. incarnata/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
+          <t>Ny lokal för arten. En del af kärret är en fin liten rikkärrsyta och det ligger i mycket trevligt skogsbetemiljö. Kärret är inte känd i rikkärrsnventeringen. Betesmarken ägs av gården Solhäll en bit söder om. Ytan med riktigt rikkärr är liten, men där växer majvivan dock i ett bra bestånd. Mot norröst blir kärret markant fattigare. Se miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,60 +1872,50 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>kärräng</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>SkFlora    673881</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alf Porenius</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Martin Stoltze</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63289365</v>
+        <v>63289366</v>
       </c>
       <c r="B13" t="n">
-        <v>98603</v>
+        <v>99802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>514</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Majnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. majalis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2071,7 +1963,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
+          <t>Carex hostiana/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,7 +1982,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>SkFlora    673873</t>
+          <t>SkFlora    673874</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2112,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53807006</v>
+        <v>63289373</v>
       </c>
       <c r="B14" t="n">
-        <v>98947</v>
+        <v>99029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,16 +2015,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>514</v>
+        <v>223578</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Majnycklar</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. majalis</t>
+          <t>Dactylorhiza incarnata var. incarnata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2142,17 +2034,17 @@
       <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fränninge, Solhälls rikkärr, Sk</t>
+          <t>850m O Ryssgård, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425049</v>
+        <v>425007</v>
       </c>
       <c r="R14" t="n">
-        <v>6177406</v>
+        <v>6177394</v>
       </c>
       <c r="S14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2176,17 +2068,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
+          <t>2001-06-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
+          <t>2001-06-19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Talrik både i kanterna och ute i kärret.</t>
+          <t>Dactylorhiza incarnata ssp. incarnata/2D6e0444/Fränninge s:n/APo/ /Alf Porenius,Dalby</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,19 +2089,33 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>kärräng</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>SkFlora    673881</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alf Porenius</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
